--- a/光伏配储项目/电价数据/2026/武江站.xlsx
+++ b/光伏配储项目/电价数据/2026/武江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5125299999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.76307</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.59153</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58441</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.5211399999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43784</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45471</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42694</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42216</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.66643</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.42436</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.41276</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40125</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39226</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.4209</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42411</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>-0.03788</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.04019</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.03727</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>-0.03357</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.0355</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.04628</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.02322</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0258</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.02491</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.0492</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01851</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.01401</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>-0.02714</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.01856</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.04011</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.04735</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.03783</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.007990000000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20003</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.28426</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.55598</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.6788999999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.56939</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43359</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.56611</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.44942</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.79875</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.62741</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63125</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.73893</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.9289500000000001</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65965</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.58333</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.72254</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.47304</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6239199999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.60366</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41627</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42599</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.69175</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99991</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.63697</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.54767</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.66623</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50461</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50493</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37957</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41775</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.48437</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.5517000000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42804</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4281</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.45102</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.26696</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.24436</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.18944</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.17437</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.11009</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.19581</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.23531</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.01538</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.15996</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03990999999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.02561</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>-0.00203</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.13385</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.18455</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.01602</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.01696</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.04196</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.03601</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.4305</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.41523</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.43449</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.49301</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.58796</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.53254</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67152</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6324</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.71936</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76563</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.47121</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.46384</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42921</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.32284</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33471</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4273</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38378</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36391</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47376</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44521</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.26081</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.25963</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.25239</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.20884</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.27185</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.44111</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.47107</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.50631</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45765</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.40827</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.46302</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.45173</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.52523</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.37147</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35687</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60876</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.57711</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59621</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46375</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42256</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48211</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.43642</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.45854</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.4441000000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.41977</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.39935</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36247</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34207</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.47724</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36623</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38475</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26085</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12505</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19788</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28214</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.20085</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30434</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56029</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.22662</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.16866</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.11012</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>-0.02363</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.03377</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>-0.00219</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.23692</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>-0.02622</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.10182</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.19418</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19477</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.10136</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.10193</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16459</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39971</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.44644</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41532</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31587</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.30344</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31565</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30617</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.22151</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04475</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.21844</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21446</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.19292</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.02871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.17941</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.09456000000000001</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.03548</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.03546</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.03743</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.03915</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03798</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04219</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04073</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.03825</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.04809</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.03979</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05799</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.00894</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03398</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09589</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46716</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39607</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35077</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.65355</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.39956</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42224</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04622</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01034</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20684</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04563</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04550999999999999</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04527</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04539</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.0436</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04167</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.01907</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04740999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04793</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19972</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30451</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.2998</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29379</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3353</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31699</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28112</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27114</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17235</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15859</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1709</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14768</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15942</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15856</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23609</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21398</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22649</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26881</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28081</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28041</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2707</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28089</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3049</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29748</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42819</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45649</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38886</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15653</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31344</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91408</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29601</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88713</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63154</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18672</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8684700000000001</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.53604</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33048</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5304099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79067</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.52964</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77266</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7772899999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87673</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8737</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49285</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39951</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20661</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87881</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49758</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45577</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43707</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45267</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41976</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38482</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4335</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33821</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5854600000000001</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60122</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.69024</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46852</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58021</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.36674</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.28044</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85894</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.7823099999999999</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7873300000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.24551</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44041</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30045</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5424600000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.26702</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30624</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30347</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4095</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41212</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41446</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39113</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.3746</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3533</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91804</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46451</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41974</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40937</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.49911</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34326</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31359</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29067</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16614</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30649</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19289</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31179</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.04198</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29967</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29001</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27645</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.44296</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42316</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.41995</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39989</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59516</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45247</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16068</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6998300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7906599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66437</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57908</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45061</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50098</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44017</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43743</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43435</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43448</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4501</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43385</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41315</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42322</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39881</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4946</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29629</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3037</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24965</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15514</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01432</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30116</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26159</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25527</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28299</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5698200000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.84733</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46429</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32333</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42159</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33459</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32428</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.3731</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3535</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28057</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.27926</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22543</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14147</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14512</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15275</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.03514</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.01041</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14129</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13609</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24715</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13662</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.17291</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.01052</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.02586</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.04048</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.10777</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10735</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12609</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.13574</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14062</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39717</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38395</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39628</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4427</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44369</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40182</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39701</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34818</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53704</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38842</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39082</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29518</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.16441</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.14764</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.01081</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20057</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29542</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31237</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28653</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24223</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30632</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34223</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38159</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.25971</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35581</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38484</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35986</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39086</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34237</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39449</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43503</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.47098</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.39116</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5211399999999999</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2495</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27351</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.20942</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.24562</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.45568</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.35456</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43453</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41675</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6898200000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5098199999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.22199</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30177</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31481</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33901</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32745</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.1594</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.20395</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.1561</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.19684</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.22662</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.22698</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.22718</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34949</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35118</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32626</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.19917</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.04661</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.04479</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.04714</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.01713</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.05856</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.04550999999999999</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.04554</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.04704999999999999</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>-0.01895</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.04852</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.04629</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.19762</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41676</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65639</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.76986</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39346</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34422</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37608</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37061</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35927</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26554</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14848</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.03548</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.03592</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19982</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.03014</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28032</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21638</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28495</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.22882</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29776</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34759</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43243</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64012</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60545</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48561</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8111</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48742</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.81276</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48943</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40056</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41851</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35983</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.4885</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5269299999999999</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47949</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.48227</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39674</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40746</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39436</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40793</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.38595</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41641</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39951</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.37569</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.39615</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.06251</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.12191</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.09681999999999999</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.04019</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.05242</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.05831</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.01108</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.19383</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.21387</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.05572</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>-0.03909000000000001</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.005059999999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.00709</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>-0.01131</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.02638</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.03056</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>-0.04438</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>-0.01569</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>-0.01535</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>-0.02073</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.02003</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>-0.02245</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.02599</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>-0.03099</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.00496</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>-0.03423</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>-0.03123</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.22945</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.22951</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36925</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49191</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43805</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50175</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50502</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.54296</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6906100000000001</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.7118</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.9222100000000001</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.53432</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.8061499999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5822999999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.5249400000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.83136</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.77011</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67214</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44139</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47167</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48169</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47613</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.46889</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41672</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42739</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44112</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45395</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39588</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3775</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37259</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37059</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36565</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.3644</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.28161</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.24771</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.27624</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.27975</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.04896</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>-0.01846</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.07128</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.19721</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.06406999999999999</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>-0.009529999999999999</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.02126</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.03044</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>-0.00546</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.03726</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.00591</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.00362</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>-0.00332</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03888</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.01949</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.04654999999999999</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.07557</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.05428</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.22646</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.23898</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43288</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41575</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38561</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40878</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40927</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37882</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.37913</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36511</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39275</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34913</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34832</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32728</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.25543</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.26872</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.26624</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.26682</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22572</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.25942</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22984</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.22698</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24918</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13947</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.22715</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.02643</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04306</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25008</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16931</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18745</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.23619</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23382</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.2355</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.20689</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.01048</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.1965</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.20514</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.18078</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.21851</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.22519</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.18013</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.22522</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33944</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33952</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.21667</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.21669</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.22374</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.29503</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.19331</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.04944</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04946</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.04987</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.04952</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03867</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04142</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.03895000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04828</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04786</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.04720000000000001</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03856</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0495</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04928</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00067</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.25238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04953</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04925</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04949</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.02164</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04947</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04945</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03774</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19017</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.24797</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2756</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.21432</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.21412</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.21282</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24826</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.22564</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.22568</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29856</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.13757</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.22604</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5382</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.22033</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2653</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27497</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.27016</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.30957</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.06520999999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.26991</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.25951</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62924</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.76198</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.75295</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.57875</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.23352</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02696</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1778</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.20012</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.17485</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.02457</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.01537</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.04778</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.02004</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04381</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.03159</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.0287</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.20882</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.20883</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.01554</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18044</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.19249</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.18756</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25656</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.22759</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.26138</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36774</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32153</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.29871</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34179</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.15602</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.52012</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5312100000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41953</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.41785</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.36078</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.23644</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.05738</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.07831</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.008230000000000001</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.04733</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.20255</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.22772</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.23481</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37876</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.41782</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.38022</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34028</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.83072</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.37563</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39484</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33149</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35801</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54025</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.23335</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.23336</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.20346</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.28655</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.20583</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.05624000000000001</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.05249</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.23473</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.03472</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.05652</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.19654</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.19555</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.20156</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.05654</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.04921</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.05735</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.05622</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.05733</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.04758</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.06239</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.24131</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.22713</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.46137</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.40521</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.44822</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.37181</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33128</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.39198</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36315</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.28992</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.19343</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.28663</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.05933</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.24101</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.24111</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.19214</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.22653</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39004</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.23217</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.23391</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.04508</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.06397</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.06167</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.06229999999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.20222</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.23621</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.04765999999999999</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.03992</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.05408</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.04881</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.20582</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.24438</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.23321</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.06587999999999999</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.20922</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.25583</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.0746</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.23899</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.40174</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.40712</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.38476</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.7445499999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.33813</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.22646</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35805</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.2242</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.26777</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.0476</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.22517</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.22413</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.23238</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.22666</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.24032</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.04219</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.05691</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.2314</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.20639</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.01896</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.04312</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.21416</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>-0.00417</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.21986</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.03904</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.07077</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.03117</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.00724</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.01858</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01146</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.02385</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.22778</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.08734</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.01185</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.02853</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.02119</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.02128</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.05827</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.06504</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.06175</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.24354</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.07163</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.07712999999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.21208</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.24058</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.23406</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.25577</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.38571</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.32883</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.22898</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.22842</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.2251</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.18038</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.22353</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.2271</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.50418</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.22632</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34753</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.31535</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.22547</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.23265</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.22659</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.22668</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.05467</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.06048</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.24295</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.20883</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22326</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.01384</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.05743</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.05535</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.19932</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.00732</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.07953</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.00656</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.00166</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.00079</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>-0.02886</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>-0.03041</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.03772</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.03399</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.05041</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.04686</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49786</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.24827</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.24548</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24415</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.29858</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38252</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.49814</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37682</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.22975</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.32413</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.32932</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.04461</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.22656</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.19408</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.03466</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.2063</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>-0.00049</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>-0.00033</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.22974</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.21884</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.22175</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.13206</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.00105</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.01827</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.02194</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.03677</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.04589</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03305</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09472</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.00801</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.03486</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>-0.02047</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.0292</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04472</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>-0.03925</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.21856</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.23347</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.004889999999999999</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.20362</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.20969</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.22831</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.22808</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.24048</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36412</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40153</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37714</v>
       </c>
     </row>
   </sheetData>
